--- a/demo-data/Customer_Master.xlsx
+++ b/demo-data/Customer_Master.xlsx
@@ -474,12 +474,12 @@
       </c>
       <c r="C5" s="13" t="inlineStr">
         <is>
-          <t>North America</t>
+          <t>Region A</t>
         </is>
       </c>
       <c r="D5" s="13" t="inlineStr">
         <is>
-          <t>Enterprise Account</t>
+          <t>Hospital / Institution</t>
         </is>
       </c>
       <c r="E5" s="13" t="inlineStr">
@@ -526,12 +526,12 @@
       </c>
       <c r="C6" s="13" t="inlineStr">
         <is>
-          <t>North America</t>
+          <t>Region A</t>
         </is>
       </c>
       <c r="D6" s="13" t="inlineStr">
         <is>
-          <t>Specialty Distributor</t>
+          <t>Retail / Pharmacy Chain</t>
         </is>
       </c>
       <c r="E6" s="13" t="inlineStr">
@@ -578,7 +578,7 @@
       </c>
       <c r="C7" s="13" t="inlineStr">
         <is>
-          <t>North America</t>
+          <t>Region A</t>
         </is>
       </c>
       <c r="D7" s="13" t="inlineStr">
@@ -630,7 +630,7 @@
       </c>
       <c r="C8" s="13" t="inlineStr">
         <is>
-          <t>EMEA</t>
+          <t>Region B</t>
         </is>
       </c>
       <c r="D8" s="13" t="inlineStr">
@@ -682,12 +682,12 @@
       </c>
       <c r="C9" s="13" t="inlineStr">
         <is>
-          <t>North America</t>
+          <t>Region A</t>
         </is>
       </c>
       <c r="D9" s="13" t="inlineStr">
         <is>
-          <t>Provider Network</t>
+          <t>Hospital / Institution</t>
         </is>
       </c>
       <c r="E9" s="13" t="inlineStr">
@@ -734,12 +734,12 @@
       </c>
       <c r="C10" s="13" t="inlineStr">
         <is>
-          <t>North America</t>
+          <t>Region A</t>
         </is>
       </c>
       <c r="D10" s="13" t="inlineStr">
         <is>
-          <t>Payer / Managed Account</t>
+          <t>Direct Corporate Account</t>
         </is>
       </c>
       <c r="E10" s="13" t="inlineStr">
@@ -786,12 +786,12 @@
       </c>
       <c r="C11" s="13" t="inlineStr">
         <is>
-          <t>EMEA</t>
+          <t>Region B</t>
         </is>
       </c>
       <c r="D11" s="13" t="inlineStr">
         <is>
-          <t>Hospital Network</t>
+          <t>Hospital / Institution</t>
         </is>
       </c>
       <c r="E11" s="13" t="inlineStr">
@@ -838,12 +838,12 @@
       </c>
       <c r="C12" s="13" t="inlineStr">
         <is>
-          <t>North America</t>
+          <t>Region A</t>
         </is>
       </c>
       <c r="D12" s="13" t="inlineStr">
         <is>
-          <t>Research Account</t>
+          <t>Direct Corporate Account</t>
         </is>
       </c>
       <c r="E12" s="13" t="inlineStr">
@@ -890,12 +890,12 @@
       </c>
       <c r="C13" s="13" t="inlineStr">
         <is>
-          <t>LATAM</t>
+          <t>Region C</t>
         </is>
       </c>
       <c r="D13" s="13" t="inlineStr">
         <is>
-          <t>Public Procurement</t>
+          <t>Buying Group</t>
         </is>
       </c>
       <c r="E13" s="13" t="inlineStr">
@@ -942,12 +942,12 @@
       </c>
       <c r="C14" s="13" t="inlineStr">
         <is>
-          <t>North America</t>
+          <t>Region A</t>
         </is>
       </c>
       <c r="D14" s="13" t="inlineStr">
         <is>
-          <t>Enterprise Account</t>
+          <t>Hospital / Institution</t>
         </is>
       </c>
       <c r="E14" s="13" t="inlineStr">
@@ -994,12 +994,12 @@
       </c>
       <c r="C15" s="13" t="inlineStr">
         <is>
-          <t>North America</t>
+          <t>Region A</t>
         </is>
       </c>
       <c r="D15" s="13" t="inlineStr">
         <is>
-          <t>Specialty Distributor</t>
+          <t>Retail / Pharmacy Chain</t>
         </is>
       </c>
       <c r="E15" s="13" t="inlineStr">
@@ -1046,12 +1046,12 @@
       </c>
       <c r="C16" s="13" t="inlineStr">
         <is>
-          <t>North America</t>
+          <t>Region A</t>
         </is>
       </c>
       <c r="D16" s="13" t="inlineStr">
         <is>
-          <t>Payer / Managed Account</t>
+          <t>Direct Corporate Account</t>
         </is>
       </c>
       <c r="E16" s="13" t="inlineStr">
@@ -1098,12 +1098,12 @@
       </c>
       <c r="C17" s="13" t="inlineStr">
         <is>
-          <t>EMEA</t>
+          <t>Region B</t>
         </is>
       </c>
       <c r="D17" s="13" t="inlineStr">
         <is>
-          <t>Hospital Network</t>
+          <t>Hospital / Institution</t>
         </is>
       </c>
       <c r="E17" s="13" t="inlineStr">
@@ -1150,12 +1150,12 @@
       </c>
       <c r="C18" s="13" t="inlineStr">
         <is>
-          <t>North America</t>
+          <t>Region A</t>
         </is>
       </c>
       <c r="D18" s="13" t="inlineStr">
         <is>
-          <t>Provider Network</t>
+          <t>Hospital / Institution</t>
         </is>
       </c>
       <c r="E18" s="13" t="inlineStr">
@@ -1202,12 +1202,12 @@
       </c>
       <c r="C19" s="13" t="inlineStr">
         <is>
-          <t>APAC</t>
+          <t>Region C</t>
         </is>
       </c>
       <c r="D19" s="13" t="inlineStr">
         <is>
-          <t>Provider Network</t>
+          <t>Hospital / Institution</t>
         </is>
       </c>
       <c r="E19" s="13" t="inlineStr">
@@ -1254,7 +1254,7 @@
       </c>
       <c r="C20" s="13" t="inlineStr">
         <is>
-          <t>EMEA</t>
+          <t>Region B</t>
         </is>
       </c>
       <c r="D20" s="13" t="inlineStr">
@@ -1306,12 +1306,12 @@
       </c>
       <c r="C21" s="13" t="inlineStr">
         <is>
-          <t>North America</t>
+          <t>Region A</t>
         </is>
       </c>
       <c r="D21" s="13" t="inlineStr">
         <is>
-          <t>Enterprise Account</t>
+          <t>Hospital / Institution</t>
         </is>
       </c>
       <c r="E21" s="13" t="inlineStr">
@@ -1358,7 +1358,7 @@
       </c>
       <c r="C22" s="13" t="inlineStr">
         <is>
-          <t>EMEA</t>
+          <t>Region B</t>
         </is>
       </c>
       <c r="D22" s="13" t="inlineStr">
@@ -1410,12 +1410,12 @@
       </c>
       <c r="C23" s="13" t="inlineStr">
         <is>
-          <t>North America</t>
+          <t>Region A</t>
         </is>
       </c>
       <c r="D23" s="13" t="inlineStr">
         <is>
-          <t>Payer / Managed Account</t>
+          <t>Direct Corporate Account</t>
         </is>
       </c>
       <c r="E23" s="13" t="inlineStr">
@@ -1462,12 +1462,12 @@
       </c>
       <c r="C24" s="13" t="inlineStr">
         <is>
-          <t>North America</t>
+          <t>Region A</t>
         </is>
       </c>
       <c r="D24" s="13" t="inlineStr">
         <is>
-          <t>Provider Network</t>
+          <t>Hospital / Institution</t>
         </is>
       </c>
       <c r="E24" s="13" t="inlineStr">
